--- a/data/trans_dic/IP16_n_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,65; 53,15</t>
+          <t>23,69; 52,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,63; 41,62</t>
+          <t>15,19; 42,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,65</t>
+          <t>2,27; 19,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,49; 58,35</t>
+          <t>26,06; 57,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,53; 51,46</t>
+          <t>22,35; 53,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 31,5</t>
+          <t>8,54; 31,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 28,95</t>
+          <t>3,22; 28,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,4; 43,72</t>
+          <t>14,66; 43,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,76; 47,26</t>
+          <t>27,18; 48,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 32,59</t>
+          <t>14,12; 32,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 19,26</t>
+          <t>4,41; 19,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,2; 44,93</t>
+          <t>23,23; 43,54</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,44; 51,8</t>
+          <t>27,2; 50,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 24,26</t>
+          <t>6,12; 23,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 26,75</t>
+          <t>8,64; 25,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 44,28</t>
+          <t>18,12; 44,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,44; 42,58</t>
+          <t>20,16; 41,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 23,16</t>
+          <t>4,93; 23,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 22,77</t>
+          <t>6,32; 23,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,95; 45,08</t>
+          <t>24,14; 44,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 43,04</t>
+          <t>26,93; 43,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 19,69</t>
+          <t>7,03; 19,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 20,78</t>
+          <t>9,34; 21,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,95; 42,28</t>
+          <t>24,42; 40,85</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,86; 47,14</t>
+          <t>18,19; 46,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 30,38</t>
+          <t>9,1; 29,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 23,73</t>
+          <t>3,92; 22,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 34,92</t>
+          <t>6,42; 35,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,63; 62,72</t>
+          <t>33,43; 60,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 19,11</t>
+          <t>3,32; 19,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 38,59</t>
+          <t>11,76; 38,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,82; 46,18</t>
+          <t>22,24; 46,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,34; 52,05</t>
+          <t>30,75; 51,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 21,41</t>
+          <t>7,84; 21,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 27,12</t>
+          <t>10,08; 25,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,02; 36,55</t>
+          <t>12,49; 36,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,86; 61,03</t>
+          <t>29,2; 62,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 26,84</t>
+          <t>7,42; 27,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 26,22</t>
+          <t>4,77; 25,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,17; 49,66</t>
+          <t>21,98; 49,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,7; 59,12</t>
+          <t>34,08; 60,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 26,41</t>
+          <t>8,41; 26,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 17,92</t>
+          <t>2,0; 17,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,79; 51,16</t>
+          <t>25,45; 51,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,15; 56,1</t>
+          <t>35,48; 54,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 22,99</t>
+          <t>10,11; 24,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 19,2</t>
+          <t>4,71; 17,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,9; 46,72</t>
+          <t>26,76; 46,84</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,2; 45,46</t>
+          <t>31,69; 45,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,31; 24,09</t>
+          <t>12,8; 23,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,99</t>
+          <t>8,15; 17,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,74; 36,68</t>
+          <t>17,21; 36,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,21; 45,73</t>
+          <t>33,45; 46,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 18,56</t>
+          <t>9,66; 19,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,58</t>
+          <t>9,32; 19,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,42; 40,25</t>
+          <t>27,46; 39,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,62; 44,5</t>
+          <t>34,24; 43,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,07; 19,5</t>
+          <t>12,31; 19,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,16</t>
+          <t>10,05; 16,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,05; 35,86</t>
+          <t>23,89; 36,22</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7762; 17441</t>
+          <t>7776; 17078</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4286; 13089</t>
+          <t>4778; 13474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>554; 4682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6846; 15078</t>
+          <t>6735; 14747</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6747; 14756</t>
+          <t>6409; 15324</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2949; 10845</t>
+          <t>2939; 10828</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>996; 6998</t>
+          <t>778; 6940</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3982; 12092</t>
+          <t>4056; 12043</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17072; 29063</t>
+          <t>16712; 29800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9580; 21465</t>
+          <t>9303; 21303</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1991; 9349</t>
+          <t>2139; 9425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12949; 24039</t>
+          <t>12429; 23294</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11845; 21574</t>
+          <t>11329; 21205</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2623; 10070</t>
+          <t>2540; 9601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3778; 11422</t>
+          <t>3690; 11004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8316; 19589</t>
+          <t>8015; 19867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8032; 17586</t>
+          <t>8326; 17231</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2034; 9338</t>
+          <t>1989; 9439</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2515; 9369</t>
+          <t>2602; 9824</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15921; 28764</t>
+          <t>15406; 28548</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22144; 35703</t>
+          <t>22340; 36184</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5806; 16108</t>
+          <t>5751; 15834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7395; 17422</t>
+          <t>7829; 18053</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28040; 45681</t>
+          <t>26389; 44135</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4746; 11861</t>
+          <t>4577; 11747</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3086; 10015</t>
+          <t>2999; 9811</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1142; 6552</t>
+          <t>1082; 6194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5407; 26915</t>
+          <t>4949; 27467</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12163; 22028</t>
+          <t>11740; 21247</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1215; 6996</t>
+          <t>1215; 7027</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3433; 10731</t>
+          <t>3270; 10577</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12988; 26289</t>
+          <t>12657; 26674</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18891; 31380</t>
+          <t>18540; 30744</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5519; 14891</t>
+          <t>5457; 14856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5768; 15028</t>
+          <t>5584; 14094</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18789; 48977</t>
+          <t>16738; 48919</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7412; 15670</t>
+          <t>7499; 15961</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3298; 11214</t>
+          <t>3099; 11419</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1791; 8598</t>
+          <t>1566; 8273</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6776; 15176</t>
+          <t>6716; 14977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12693; 22947</t>
+          <t>13229; 23501</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3701; 12472</t>
+          <t>3971; 12370</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>575; 5401</t>
+          <t>604; 5375</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8382; 17295</t>
+          <t>8603; 17557</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22671; 36180</t>
+          <t>22882; 35146</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9284; 20468</t>
+          <t>9002; 21707</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3214; 12084</t>
+          <t>2966; 10908</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17314; 30075</t>
+          <t>17228; 30149</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39093; 56965</t>
+          <t>39714; 57125</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19656; 35575</t>
+          <t>18904; 35340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11295; 22928</t>
+          <t>10393; 22664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29750; 65193</t>
+          <t>30581; 64467</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47798; 65808</t>
+          <t>48140; 66271</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15011; 29427</t>
+          <t>15323; 30154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11687; 24135</t>
+          <t>11485; 24391</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49952; 73332</t>
+          <t>50027; 72760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93218; 119813</t>
+          <t>92190; 118258</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36973; 59728</t>
+          <t>37709; 60077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25228; 43032</t>
+          <t>25200; 42264</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86563; 129050</t>
+          <t>85984; 130359</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16_n_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>37,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>26,73%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,69; 52,04</t>
+          <t>23,68; 53,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,19; 42,85</t>
+          <t>9,69; 32,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 19,22</t>
+          <t>3,34; 29,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,06; 57,07</t>
+          <t>15,12; 44,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 53,44</t>
+          <t>25,6; 52,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 31,46</t>
+          <t>13,78; 43,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 28,71</t>
+          <t>2,3; 18,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,66; 43,54</t>
+          <t>27,59; 58,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,18; 48,46</t>
+          <t>27,18; 46,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,12; 32,34</t>
+          <t>14,4; 32,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 19,42</t>
+          <t>4,56; 19,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,23; 43,54</t>
+          <t>25,88; 47,36</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35,08%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>39,04%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,03%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,9%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,2; 50,92</t>
+          <t>19,17; 41,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 23,13</t>
+          <t>5,14; 24,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 25,77</t>
+          <t>6,2; 23,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,12; 44,91</t>
+          <t>24,1; 45,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,16; 41,72</t>
+          <t>28,61; 52,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 23,41</t>
+          <t>5,99; 24,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 23,88</t>
+          <t>8,43; 25,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,14; 44,74</t>
+          <t>23,14; 49,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,93; 43,62</t>
+          <t>26,29; 43,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 19,35</t>
+          <t>7,54; 19,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 21,53</t>
+          <t>8,8; 20,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,42; 40,85</t>
+          <t>26,62; 43,56</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47,28%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33,16%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>31,99%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18,13%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,96%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 46,68</t>
+          <t>34,99; 61,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 29,76</t>
+          <t>3,32; 19,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 22,43</t>
+          <t>13,38; 39,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 35,64</t>
+          <t>22,17; 46,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,43; 60,49</t>
+          <t>20,6; 47,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 19,2</t>
+          <t>9,76; 31,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,76; 38,04</t>
+          <t>4,1; 25,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,24; 46,86</t>
+          <t>20,84; 42,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,75; 51,0</t>
+          <t>30,73; 50,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 21,36</t>
+          <t>7,23; 20,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 25,43</t>
+          <t>10,27; 27,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 36,51</t>
+          <t>24,08; 40,97</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37,79%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>44,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,37%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 62,16</t>
+          <t>31,77; 58,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 27,33</t>
+          <t>8,85; 26,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 25,23</t>
+          <t>2,0; 17,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,98; 49,01</t>
+          <t>24,97; 53,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,08; 60,54</t>
+          <t>29,14; 61,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 26,19</t>
+          <t>8,36; 27,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 17,83</t>
+          <t>4,99; 26,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,45; 51,93</t>
+          <t>21,0; 49,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,48; 54,5</t>
+          <t>35,62; 55,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 24,39</t>
+          <t>10,4; 23,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 17,33</t>
+          <t>5,27; 18,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,76; 46,84</t>
+          <t>25,58; 47,22</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>38,26%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,69; 45,59</t>
+          <t>33,39; 46,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,93</t>
+          <t>9,62; 18,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 17,78</t>
+          <t>9,34; 19,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 36,28</t>
+          <t>27,97; 40,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,45; 46,05</t>
+          <t>31,22; 45,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 19,02</t>
+          <t>13,13; 23,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 19,79</t>
+          <t>8,02; 17,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,46; 39,93</t>
+          <t>28,14; 40,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,24; 43,93</t>
+          <t>34,4; 44,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 19,62</t>
+          <t>12,48; 19,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,86</t>
+          <t>9,91; 17,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,89; 36,22</t>
+          <t>30,27; 39,25</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10503</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6876</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12286</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8405</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10721</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10503</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6411</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18109</t>
+          <t>18180</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7776; 17078</t>
+          <t>6790; 15412</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4778; 13474</t>
+          <t>3336; 11254</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>554; 4682</t>
+          <t>807; 7106</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6735; 14747</t>
+          <t>3723; 10920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6409; 15324</t>
+          <t>8402; 17187</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2939; 10828</t>
+          <t>4332; 13550</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>778; 6940</t>
+          <t>560; 4526</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4056; 12043</t>
+          <t>7259; 15326</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16712; 29800</t>
+          <t>16715; 28737</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9303; 21303</t>
+          <t>9486; 21394</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2139; 9425</t>
+          <t>2212; 9509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12429; 23294</t>
+          <t>13181; 24119</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12447</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5254</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19806</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16259</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5407</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6790</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13751</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12447</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4675</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5254</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>32318</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11329; 21205</t>
+          <t>7919; 17145</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2540; 9601</t>
+          <t>2072; 9866</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3690; 11004</t>
+          <t>2550; 9818</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8015; 19867</t>
+          <t>13609; 25945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8326; 17231</t>
+          <t>11915; 21788</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1989; 9439</t>
+          <t>2488; 10096</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2602; 9824</t>
+          <t>3600; 11046</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15406; 28548</t>
+          <t>8363; 17714</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22340; 36184</t>
+          <t>21810; 36094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5751; 15834</t>
+          <t>6170; 16197</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7829; 18053</t>
+          <t>7377; 17220</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26389; 44135</t>
+          <t>24649; 40334</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16606</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6545</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17363</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8049</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5975</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3026</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15648</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16606</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3309</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>32946</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4577; 11747</t>
+          <t>12291; 21610</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2999; 9811</t>
+          <t>1217; 7048</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1082; 6194</t>
+          <t>3721; 10975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4949; 27467</t>
+          <t>11605; 24483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11740; 21247</t>
+          <t>5183; 12026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1215; 7027</t>
+          <t>3218; 10240</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3270; 10577</t>
+          <t>1131; 6989</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12657; 26674</t>
+          <t>10592; 21504</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18540; 30744</t>
+          <t>18526; 30458</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5457; 14856</t>
+          <t>5027; 14071</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5584; 14094</t>
+          <t>5691; 14970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16738; 48919</t>
+          <t>24841; 42270</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17708</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7450</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11910</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11343</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6683</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4382</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10543</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17708</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7450</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>22138</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7499; 15961</t>
+          <t>12331; 22658</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3099; 11419</t>
+          <t>4178; 12686</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1566; 8273</t>
+          <t>603; 5295</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6716; 14977</t>
+          <t>7869; 16916</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13229; 23501</t>
+          <t>7482; 15888</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3971; 12370</t>
+          <t>3493; 11493</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>604; 5375</t>
+          <t>1635; 8796</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8603; 17557</t>
+          <t>6242; 14752</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22882; 35146</t>
+          <t>22972; 35711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9002; 21707</t>
+          <t>9260; 21237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2966; 10908</t>
+          <t>3315; 11606</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17228; 30149</t>
+          <t>15667; 28920</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>57263</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>47937</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>26470</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>15989</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21844</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39714; 57125</t>
+          <t>48060; 66398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18904; 35340</t>
+          <t>15257; 30041</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10393; 22664</t>
+          <t>11520; 23909</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30581; 64467</t>
+          <t>46133; 66628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48140; 66271</t>
+          <t>39115; 57055</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15323; 30154</t>
+          <t>19392; 34820</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11485; 24391</t>
+          <t>10223; 22667</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50027; 72760</t>
+          <t>40244; 58311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92190; 118258</t>
+          <t>92603; 119116</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37709; 60077</t>
+          <t>38212; 60635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25200; 42264</t>
+          <t>24849; 42911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85984; 130359</t>
+          <t>93209; 120878</t>
         </is>
       </c>
     </row>
